--- a/análise de dados/dados demográficos dos estudantes.xlsx
+++ b/análise de dados/dados demográficos dos estudantes.xlsx
@@ -1,23 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julio\Desktop\clean-code\análise de dados\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B878A1C7-17D8-41AE-92B0-F88B87C8C00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="gaficos" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="estatisticas" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="base de dados" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="dados" sheetId="4" r:id="rId8"/>
+    <sheet name="gaficos" sheetId="1" r:id="rId1"/>
+    <sheet name="estatisticas" sheetId="2" r:id="rId2"/>
+    <sheet name="base de dados" sheetId="3" r:id="rId3"/>
+    <sheet name="dados" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="6" r:id="rId5"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="68">
   <si>
     <t>participante</t>
   </si>
@@ -142,9 +165,6 @@
     <t>TABELA GENERO DOS USUARIOS</t>
   </si>
   <si>
-    <t>COUNT de participante</t>
-  </si>
-  <si>
     <t>TABELA PERIODO DOS PARTICIPANTES</t>
   </si>
   <si>
@@ -219,29 +239,38 @@
   <si>
     <t>TABELA FONTES CLEAN CODE</t>
   </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>COUNT of participante</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -252,7 +281,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -285,124 +314,205 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="8">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="41">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="6" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="28">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF356854"/>
           <bgColor rgb="FF356854"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
     <dxf>
       <border>
@@ -420,70 +530,309 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="7">
-    <tableStyle count="4" pivot="0" name="base de dados-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="base de dados-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="24"/>
+      <tableStyleElement type="headerRow" dxfId="27"/>
+      <tableStyleElement type="firstRowStripe" dxfId="26"/>
+      <tableStyleElement type="secondRowStripe" dxfId="25"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="estatisticas-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="estatisticas-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="20"/>
+      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="22"/>
+      <tableStyleElement type="secondRowStripe" dxfId="21"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="estatisticas-style 2">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="estatisticas-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="19"/>
+      <tableStyleElement type="firstRowStripe" dxfId="18"/>
+      <tableStyleElement type="secondRowStripe" dxfId="17"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="estatisticas-style 3">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="estatisticas-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="estatisticas-style 4">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="estatisticas-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="estatisticas-style 5">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="estatisticas-style 5" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" dxfId="5"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="estatisticas-style 6">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="estatisticas-style 6" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.07428580729166669"/>
+          <c:x val="7.4285807291666686E-2"/>
           <c:y val="0.12630208333333334"/>
-          <c:w val="0.8947975260416668"/>
+          <c:w val="0.89479752604166685"/>
           <c:h val="0.7751803964510332"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -498,17 +847,83 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$12:$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>periodo</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$12:$B$18</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C3FB-4183-A96F-AA208A7DDF3B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -524,17 +939,83 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$12:$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>periodo</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$12:$B$18</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C3FB-4183-A96F-AA208A7DDF3B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -542,19 +1023,79 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$10:$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>TABELA PERIODO DOS PARTICIPANTES</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$12:$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>periodo</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$12:$B$18</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C3FB-4183-A96F-AA208A7DDF3B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -562,20 +1103,89 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$C$10:$C$11</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>TABELA PERIODO DOS PARTICIPANTES</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$12:$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>periodo</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$C$12:$C$18</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.4516129032258063E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.6774193548387094E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16129032258064516</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.4516129032258063E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16129032258064516</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.41935483870967744</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C3FB-4183-A96F-AA208A7DDF3B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1193222418"/>
         <c:axId val="1089542937"/>
       </c:barChart>
@@ -617,6 +1227,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
@@ -634,9 +1245,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1089542937"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="1089542937"/>
@@ -705,9 +1322,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1193222418"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -725,27 +1345,48 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de participantes</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -756,17 +1397,71 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$32:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>menos de 6 meses</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6 meses - 1 ano</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1-2 anos</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2-4 anos</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>mais de 4 anos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$32:$B$36</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4A75-4FF0-B27D-EEF6818A9569}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -782,17 +1477,71 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$32:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>menos de 6 meses</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6 meses - 1 ano</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1-2 anos</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2-4 anos</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>mais de 4 anos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$32:$B$36</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4A75-4FF0-B27D-EEF6818A9569}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -800,19 +1549,67 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de participantes</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$32:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>menos de 6 meses</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6 meses - 1 ano</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1-2 anos</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2-4 anos</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>mais de 4 anos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$32:$B$36</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4A75-4FF0-B27D-EEF6818A9569}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -820,20 +1617,77 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$C$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>representação em porcentagem</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$32:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>menos de 6 meses</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6 meses - 1 ano</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1-2 anos</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2-4 anos</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>mais de 4 anos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$C$32:$C$36</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26923076923076922</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73076923076923073</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4A75-4FF0-B27D-EEF6818A9569}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="691055883"/>
         <c:axId val="1701025141"/>
       </c:barChart>
@@ -875,6 +1729,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
@@ -892,9 +1747,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1701025141"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="1701025141"/>
@@ -963,9 +1824,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="691055883"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -983,16 +1847,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1022,25 +1898,34 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.06967482793898812"/>
+          <c:x val="6.9674827938988118E-2"/>
           <c:y val="0.18629807692307693"/>
-          <c:w val="0.8993727911086311"/>
-          <c:h val="0.7204326923076922"/>
+          <c:w val="0.89937279110863111"/>
+          <c:h val="0.72043269230769225"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1051,17 +1936,65 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$40:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>nenhuma</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>basica</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>intermediaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>avancada</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$40:$B$43</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-53A6-4A55-942C-4BE9545C3979}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1069,6 +2002,12 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1079,17 +2018,65 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$40:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>nenhuma</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>basica</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>intermediaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>avancada</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$40:$B$43</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-53A6-4A55-942C-4BE9545C3979}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1097,19 +2084,61 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$40:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>nenhuma</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>basica</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>intermediaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>avancada</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$40:$B$43</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-53A6-4A55-942C-4BE9545C3979}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1117,20 +2146,71 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$C$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidadade em porcentagem</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$40:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>nenhuma</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>basica</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>intermediaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>avancada</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$C$40:$C$43</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.34375</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.125E-2</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-53A6-4A55-942C-4BE9545C3979}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="112392453"/>
         <c:axId val="433597847"/>
       </c:barChart>
@@ -1155,15 +2235,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1172,6 +2244,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
@@ -1189,9 +2262,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="433597847"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="433597847"/>
@@ -1225,15 +2304,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1260,9 +2331,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="112392453"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1280,16 +2354,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1319,16 +2405,25 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1339,17 +2434,71 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$47:$A$51</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>nunca</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>raramente</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>as vezes</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>frequentemente</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>muito frequentemente</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$47:$B$51</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E61A-431C-A00B-AAFC4B463C6A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1357,6 +2506,12 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1367,17 +2522,71 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$47:$A$51</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>nunca</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>raramente</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>as vezes</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>frequentemente</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>muito frequentemente</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$47:$B$51</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E61A-431C-A00B-AAFC4B463C6A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1385,19 +2594,67 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$47:$A$51</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>nunca</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>raramente</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>as vezes</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>frequentemente</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>muito frequentemente</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$47:$B$51</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E61A-431C-A00B-AAFC4B463C6A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1405,20 +2662,77 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$C$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidadade em porcentagem</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$47:$A$51</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>nunca</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>raramente</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>as vezes</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>frequentemente</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>muito frequentemente</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$C$47:$C$51</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6.25E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.53125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E61A-431C-A00B-AAFC4B463C6A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1453478849"/>
         <c:axId val="699231251"/>
       </c:barChart>
@@ -1443,15 +2757,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1460,6 +2766,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
@@ -1477,9 +2784,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="699231251"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="699231251"/>
@@ -1513,15 +2826,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1548,9 +2853,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1453478849"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1568,16 +2876,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1607,10 +2927,21 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:view3D>
       <c:rotX val="50"/>
-      <c:perspective val="0"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="1"/>
     </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
       <c:pie3DChart>
@@ -1621,44 +2952,76 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$54</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="4285F4"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-1BE9-40F8-9F2F-9A816F7A95A6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="EA4335"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-1BE9-40F8-9F2F-9A816F7A95A6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
-          <c:dLbls>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$55:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>sim</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>nao</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$55:$B$56</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1BE9-40F8-9F2F-9A816F7A95A6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1667,6 +3030,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
       </c:pie3DChart>
     </c:plotArea>
@@ -1685,16 +3049,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1724,10 +3100,21 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:view3D>
       <c:rotX val="50"/>
-      <c:perspective val="0"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="1"/>
     </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
       <c:pie3DChart>
@@ -1738,60 +3125,116 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$C$59</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidadade em porcentagem</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B861-4AEC-B689-72C15C2EF5D8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B861-4AEC-B689-72C15C2EF5D8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent4"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-B861-4AEC-B689-72C15C2EF5D8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="34A853"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-B861-4AEC-B689-72C15C2EF5D8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
-          <c:dLbls>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$60:$A$63</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>nenhuma</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>basica</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>intermediaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>avancada</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$C$60:$C$63</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.125E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.46875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-B861-4AEC-B689-72C15C2EF5D8}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1800,6 +3243,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
       </c:pie3DChart>
     </c:plotArea>
@@ -1818,16 +3262,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1857,25 +3313,34 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.07141754957231723"/>
+          <c:x val="7.1417549572317232E-2"/>
           <c:y val="0.21685393258426966"/>
-          <c:w val="0.8976337723561432"/>
-          <c:h val="0.5089417123068526"/>
+          <c:w val="0.89763377235614317"/>
+          <c:h val="0.50894171230685259"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1886,17 +3351,77 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$77:$A$82</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>artigos/blogs</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>documentacao/tutorial</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>livro clean code</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>disciplina academica</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>youtube/instagram</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>nao</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$77:$B$82</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BF79-4D99-A499-BCC6AB4AC175}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1904,6 +3429,12 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1914,17 +3445,77 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$77:$A$82</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>artigos/blogs</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>documentacao/tutorial</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>livro clean code</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>disciplina academica</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>youtube/instagram</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>nao</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$77:$B$82</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BF79-4D99-A499-BCC6AB4AC175}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1932,19 +3523,73 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$B$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidade de alunos</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$77:$A$82</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>artigos/blogs</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>documentacao/tutorial</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>livro clean code</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>disciplina academica</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>youtube/instagram</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>nao</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$B$77:$B$82</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BF79-4D99-A499-BCC6AB4AC175}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1952,20 +3597,83 @@
           <c:tx>
             <c:strRef>
               <c:f>estatisticas!$C$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quantidadade em porcentagem</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>estatisticas!$A$77:$A$82</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>artigos/blogs</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>documentacao/tutorial</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>livro clean code</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>disciplina academica</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>youtube/instagram</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>nao</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>estatisticas!$C$77:$C$82</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.21739130434782608</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17391304347826086</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13043478260869565</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.2608695652173913</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.3478260869565216E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.17391304347826086</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-BF79-4D99-A499-BCC6AB4AC175}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1977210901"/>
         <c:axId val="622586106"/>
       </c:barChart>
@@ -1990,15 +3698,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2007,6 +3707,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
@@ -2024,9 +3725,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="622586106"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="622586106"/>
@@ -2060,15 +3767,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2095,9 +3794,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1977210901"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2115,16 +3817,24 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2133,9 +3843,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5924550" cy="3657600"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1" title="Gráfico"/>
+        <xdr:cNvPr id="2" name="Chart 1" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2144,7 +3860,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2158,9 +3874,15 @@
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 3" title="Gráfico"/>
+        <xdr:cNvPr id="3" name="Chart 3" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2169,7 +3891,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2183,9 +3905,15 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6076950" cy="3762375"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 4" title="Gráfico"/>
+        <xdr:cNvPr id="4" name="Chart 4" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2194,7 +3922,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2208,9 +3936,15 @@
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 5" title="Gráfico"/>
+        <xdr:cNvPr id="5" name="Chart 5" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2219,7 +3953,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2233,9 +3967,15 @@
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 6" title="Gráfico"/>
+        <xdr:cNvPr id="6" name="Chart 6" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2244,7 +3984,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2258,9 +3998,15 @@
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6257925" cy="3876675"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 7" title="Gráfico"/>
+        <xdr:cNvPr id="7" name="Chart 7" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2269,7 +4015,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2279,7 +4025,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2288,9 +4034,15 @@
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6124575" cy="4238625"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2" title="Gráfico"/>
+        <xdr:cNvPr id="2" name="Chart 2" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2299,7 +4051,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2308,373 +4060,543 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="julio candeia" refreshedDate="46247.668958912036" refreshedVersion="7" recordCount="31" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:K32" sheet="base de dados"/>
+    <worksheetSource ref="A1:K33" sheet="base de dados"/>
   </cacheSource>
-  <cacheFields>
+  <cacheFields count="11">
     <cacheField name="participante" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
-        <n v="1.0"/>
-        <n v="2.0"/>
-        <n v="3.0"/>
-        <n v="4.0"/>
-        <n v="5.0"/>
-        <n v="6.0"/>
-        <n v="7.0"/>
-        <n v="8.0"/>
-        <n v="9.0"/>
-        <n v="10.0"/>
-        <n v="11.0"/>
-        <n v="12.0"/>
-        <n v="13.0"/>
-        <n v="14.0"/>
-        <n v="15.0"/>
-        <n v="16.0"/>
-        <n v="17.0"/>
-        <n v="18.0"/>
-        <n v="19.0"/>
-        <n v="20.0"/>
-        <n v="21.0"/>
-        <n v="22.0"/>
-        <n v="23.0"/>
-        <n v="24.0"/>
-        <n v="25.0"/>
-        <n v="26.0"/>
-        <n v="27.0"/>
-        <n v="28.0"/>
-        <n v="29.0"/>
-        <n v="30.0"/>
-        <n v="31.0"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="31"/>
     </cacheField>
     <cacheField name="idade" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
-        <n v="22.0"/>
-        <n v="25.0"/>
-        <n v="20.0"/>
-        <n v="23.0"/>
-        <n v="43.0"/>
-        <n v="19.0"/>
-        <n v="29.0"/>
-        <n v="32.0"/>
-        <n v="24.0"/>
-        <n v="27.0"/>
-        <n v="21.0"/>
-        <n v="30.0"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="19" maxValue="43"/>
     </cacheField>
     <cacheField name="genero" numFmtId="0">
-      <sharedItems>
+      <sharedItems count="2">
         <s v="feminino"/>
         <s v="masculino"/>
       </sharedItems>
     </cacheField>
     <cacheField name="periodo" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
-        <n v="8.0"/>
-        <n v="9.0"/>
-        <n v="3.0"/>
-        <n v="4.0"/>
-        <n v="6.0"/>
-        <n v="7.0"/>
-        <n v="10.0"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="10" count="7">
+        <n v="8"/>
+        <n v="9"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="10"/>
       </sharedItems>
     </cacheField>
     <cacheField name="quanto tempo você programa" numFmtId="0">
-      <sharedItems>
-        <s v="2-4 anos"/>
-        <s v="mais de 4 anos"/>
-        <s v="1-2 anos"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="nivel de experiência com python" numFmtId="0">
-      <sharedItems>
-        <s v="basica"/>
-        <s v="intermediaria"/>
-        <s v="avancada"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="frequência que usa python" numFmtId="0">
-      <sharedItems>
-        <s v="as vezes"/>
-        <s v="raramente"/>
-        <s v="frequentemente"/>
-        <s v="nunca"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="conhece clean code" numFmtId="0">
-      <sharedItems>
-        <s v="sim"/>
-        <s v="nao"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="nivel em Clean Code" numFmtId="0">
-      <sharedItems>
-        <s v="basica"/>
-        <s v="intermediaria"/>
-        <s v="nenhuma"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="o que leu sobre Clean Code" numFmtId="0">
-      <sharedItems>
-        <s v="artigos/blog; disciplina academica"/>
-        <s v="artigos/blogs; documentacao/tutorial"/>
-        <s v="artigos/blogs; documentacao/tutorial; livro clean code"/>
-        <s v="artigos/blogs; documentacao/tutorial; disciplina academica"/>
-        <s v="artigos/blogs; documentacao/tutorial; cursos "/>
-        <s v="nao"/>
-        <s v="artigos/blogs"/>
-        <s v="documentacao/tutorial"/>
-        <s v="disciplina academica"/>
-        <s v="youtube/instagram"/>
-        <s v="livro clean code"/>
-        <s v="artigos/blogs; documentacao/tutorial; livro clean code; disciplina academica"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="importância da legibilidade no desenvolvimento" numFmtId="0">
-      <sharedItems>
-        <s v="muito importante"/>
-        <s v="importante"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="31">
+  <r>
+    <n v="1"/>
+    <n v="22"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="as vezes"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="artigos/blog; disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <n v="25"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="mais de 4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="artigos/blog; disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="artigos/blogs; documentacao/tutorial"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="mais de 4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="artigos/blogs; documentacao/tutorial; livro clean code"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <n v="20"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="1-2 anos"/>
+    <s v="intermediaria"/>
+    <s v="frequentemente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="artigos/blogs; documentacao/tutorial"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <n v="23"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="2-4 anos"/>
+    <s v="intermediaria"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="artigos/blogs; documentacao/tutorial; disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <n v="43"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="artigos/blogs; documentacao/tutorial; cursos "/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <n v="19"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="1-2 anos"/>
+    <s v="basica"/>
+    <s v="nunca"/>
+    <s v="nao"/>
+    <s v="nenhuma"/>
+    <s v="nao"/>
+    <s v="importante"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="intermediaria"/>
+    <s v="as vezes"/>
+    <s v="nao"/>
+    <s v="basica"/>
+    <s v="artigos/blogs"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <n v="23"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="documentacao/tutorial"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="intermediaria"/>
+    <s v="frequentemente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="youtube/instagram"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <n v="22"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="avancada"/>
+    <s v="frequentemente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="artigos/blogs"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="intermediaria"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="artigos/blogs"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <n v="24"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="1-2 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <n v="27"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="mais de 4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="artigos/blogs"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <n v="23"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="2-4 anos"/>
+    <s v="intermediaria"/>
+    <s v="frequentemente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="livro clean code"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="1-2 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="livro clean code"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <n v="21"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="1-2 anos"/>
+    <s v="intermediaria"/>
+    <s v="as vezes"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="nao"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <n v="20"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="1-2 anos"/>
+    <s v="intermediaria"/>
+    <s v="as vezes"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="nao"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <n v="22"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="nunca"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="documentacao/tutorial"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <n v="21"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="documentacao/tutorial"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="artigos/blogs"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="mais de 4 anos"/>
+    <s v="intermediaria"/>
+    <s v="as vezes"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="artigos/blogs; documentacao/tutorial; livro clean code; disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <n v="24"/>
+    <x v="1"/>
+    <x v="6"/>
+    <s v="mais de 4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="as vezes"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <n v="21"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="as vezes"/>
+    <s v="sim"/>
+    <s v="basica"/>
+    <s v="disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="2-4 anos"/>
+    <s v="intermediaria"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="nao"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <n v="23"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="2-4 anos"/>
+    <s v="basica"/>
+    <s v="raramente"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="livro clean code"/>
+    <s v="muito importante"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="1-2 anos"/>
+    <s v="basica"/>
+    <s v="as vezes"/>
+    <s v="sim"/>
+    <s v="intermediaria"/>
+    <s v="artigos/blog; disciplina academica"/>
+    <s v="muito importante"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="estatisticas" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
-  <location ref="A3:C5" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
-  <pivotFields>
-    <pivotField name="participante" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="idade" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="estatisticas" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField name="participante" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="idade" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="genero" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
-      <items>
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="periodo" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="quanto tempo você programa" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="nivel de experiência com python" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="frequência que usa python" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="conhece clean code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="nivel em Clean Code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="o que leu sobre Clean Code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="importância da legibilidade no desenvolvimento" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField name="periodo" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="quanto tempo você programa" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="nivel de experiência com python" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="frequência que usa python" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="conhece clean code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="nivel em Clean Code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="o que leu sobre Clean Code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="importância da legibilidade no desenvolvimento" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
   </pivotFields>
-  <rowFields>
+  <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <colFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <dataFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
     <dataField name="COUNT of participante" fld="0" subtotal="countNums" baseField="0"/>
     <dataField name="COUNT of participante" fld="0" subtotal="countNums" showDataAs="percentOfTotal" baseField="0" numFmtId="10"/>
   </dataFields>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="estatisticas 2" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
-  <location ref="A11:C18" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
-  <pivotFields>
-    <pivotField name="participante" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="idade" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="genero" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000001000000}" name="estatisticas 2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" rowGrandTotals="0" compact="0" compactData="0">
+  <location ref="A11:C19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField name="participante" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="idade" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="genero" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="periodo" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
-      <items>
+      <items count="8">
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
@@ -2685,171 +4607,151 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="quanto tempo você programa" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="nivel de experiência com python" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="frequência que usa python" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="conhece clean code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="nivel em Clean Code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="o que leu sobre Clean Code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="importância da legibilidade no desenvolvimento" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField name="quanto tempo você programa" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="nivel de experiência com python" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="frequência que usa python" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="conhece clean code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="nivel em Clean Code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="o que leu sobre Clean Code" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="importância da legibilidade no desenvolvimento" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
   </pivotFields>
-  <rowFields>
+  <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <colFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <dataFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
     <dataField name="COUNT of participante" fld="0" subtotal="countNums" baseField="0"/>
     <dataField name="percentual" fld="0" subtotal="countNums" showDataAs="percentOfTotal" baseField="0" numFmtId="10"/>
   </dataFields>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:C36" displayName="tebela_tempo_de_programação" name="tebela_tempo_de_programação" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tebela_tempo_de_programação" displayName="tebela_tempo_de_programação" ref="A31:C36">
   <tableColumns count="3">
-    <tableColumn name="TABELA TEMPO DE PROGRAMACAO" id="1"/>
-    <tableColumn name="quantidade de participantes" id="2"/>
-    <tableColumn name="representação em porcentagem" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TABELA TEMPO DE PROGRAMACAO"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="quantidade de participantes"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="representação em porcentagem"/>
   </tableColumns>
-  <tableStyleInfo name="estatisticas-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="estatisticas-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A39:C43" displayName="Tabela_2" name="Tabela_2" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela_2" displayName="Tabela_2" ref="A39:C43">
   <tableColumns count="3">
-    <tableColumn name="TABELA EXPERIENCIA EM PYTHON" id="1"/>
-    <tableColumn name="quantidade de alunos" id="2"/>
-    <tableColumn name="quantidadade em porcentagem" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="TABELA EXPERIENCIA EM PYTHON"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="quantidade de alunos"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="quantidadade em porcentagem"/>
   </tableColumns>
-  <tableStyleInfo name="estatisticas-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="estatisticas-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A46:C51" displayName="Tabela_3" name="Tabela_3" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela_3" displayName="Tabela_3" ref="A46:C51">
   <tableColumns count="3">
-    <tableColumn name="TABELA FREQUENCIA QUE USA PYTHON" id="1"/>
-    <tableColumn name="quantidade de alunos" id="2"/>
-    <tableColumn name="quantidadade em porcentagem" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="TABELA FREQUENCIA QUE USA PYTHON"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="quantidade de alunos"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="quantidadade em porcentagem"/>
   </tableColumns>
-  <tableStyleInfo name="estatisticas-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="estatisticas-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A54:C56" displayName="Tabela_4" name="Tabela_4" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabela_4" displayName="Tabela_4" ref="A54:C56">
   <tableColumns count="3">
-    <tableColumn name="TABELA CONHECE CLEAN CODE?" id="1"/>
-    <tableColumn name="quantidade de alunos" id="2"/>
-    <tableColumn name="quantidadade em porcentagem" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="TABELA CONHECE CLEAN CODE?"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="quantidade de alunos"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="quantidadade em porcentagem"/>
   </tableColumns>
-  <tableStyleInfo name="estatisticas-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="estatisticas-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A59:C63" displayName="Tabela_5" name="Tabela_5" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabela_5" displayName="Tabela_5" ref="A59:C63">
   <tableColumns count="3">
-    <tableColumn name="TABELA NIVEL DE CLEAN CODE" id="1"/>
-    <tableColumn name="quantidade de alunos" id="2"/>
-    <tableColumn name="quantidadade em porcentagem" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="TABELA NIVEL DE CLEAN CODE"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="quantidade de alunos"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="quantidadade em porcentagem"/>
   </tableColumns>
-  <tableStyleInfo name="estatisticas-style 5" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="estatisticas-style 5" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A76:C82" displayName="Tabela_6" name="Tabela_6" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabela_6" displayName="Tabela_6" ref="A76:C82">
   <tableColumns count="3">
-    <tableColumn name="TABELA FONTES CLEAN CODE" id="1"/>
-    <tableColumn name="quantidade de alunos" id="2"/>
-    <tableColumn name="quantidadade em porcentagem" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="TABELA FONTES CLEAN CODE"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="quantidade de alunos"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="quantidadade em porcentagem"/>
   </tableColumns>
-  <tableStyleInfo name="estatisticas-style 6" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="estatisticas-style 6" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K32" displayName="Tabela_1" name="Tabela_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabela_1" displayName="Tabela_1" ref="A1:K33">
   <tableColumns count="11">
-    <tableColumn name="participante" id="1"/>
-    <tableColumn name="idade" id="2"/>
-    <tableColumn name="genero" id="3"/>
-    <tableColumn name="periodo" id="4"/>
-    <tableColumn name="quanto tempo você programa" id="5"/>
-    <tableColumn name="nivel de experiência com python" id="6"/>
-    <tableColumn name="frequência que usa python" id="7"/>
-    <tableColumn name="conhece clean code" id="8"/>
-    <tableColumn name="nivel em Clean Code" id="9"/>
-    <tableColumn name="o que leu sobre Clean Code" id="10"/>
-    <tableColumn name="importância da legibilidade no desenvolvimento" id="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="participante"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="idade"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="genero"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="periodo"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="quanto tempo você programa"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="nivel de experiência com python"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="frequência que usa python"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="conhece clean code"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="nivel em Clean Code"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="o que leu sobre Clean Code"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="importância da legibilidade no desenvolvimento"/>
   </tableColumns>
-  <tableStyleInfo name="base de dados-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="base de dados-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -3039,555 +4941,689 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A2:D82"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="36.0"/>
-    <col customWidth="1" min="2" max="2" width="26.13"/>
-    <col customWidth="1" min="3" max="3" width="32.38"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="23">
-      <c r="A23" s="10" t="s">
+      <c r="B2" s="26"/>
+    </row>
+    <row r="3" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="29"/>
+      <c r="B3" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="31"/>
+    </row>
+    <row r="4" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="33">
+        <v>8</v>
+      </c>
+      <c r="C5" s="34">
+        <v>0.25806451612903225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="36">
+        <v>23</v>
+      </c>
+      <c r="C6" s="37">
+        <v>0.74193548387096775</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+    </row>
+    <row r="11" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="31"/>
+    </row>
+    <row r="12" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="29">
+        <v>3</v>
+      </c>
+      <c r="B13" s="33">
+        <v>2</v>
+      </c>
+      <c r="C13" s="34">
+        <v>6.4516129032258063E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="38">
+        <v>4</v>
+      </c>
+      <c r="B14" s="39">
+        <v>3</v>
+      </c>
+      <c r="C14" s="40">
+        <v>9.6774193548387094E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="38">
+        <v>6</v>
+      </c>
+      <c r="B15" s="39">
+        <v>5</v>
+      </c>
+      <c r="C15" s="40">
+        <v>0.16129032258064516</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="38">
+        <v>7</v>
+      </c>
+      <c r="B16" s="39">
+        <v>2</v>
+      </c>
+      <c r="C16" s="40">
+        <v>6.4516129032258063E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="38">
+        <v>8</v>
+      </c>
+      <c r="B17" s="39">
+        <v>5</v>
+      </c>
+      <c r="C17" s="40">
+        <v>0.16129032258064516</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="38">
+        <v>9</v>
+      </c>
+      <c r="B18" s="39">
+        <v>13</v>
+      </c>
+      <c r="C18" s="40">
+        <v>0.41935483870967744</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="35">
+        <v>10</v>
+      </c>
+      <c r="B19" s="36">
+        <v>1</v>
+      </c>
+      <c r="C19" s="37">
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="26"/>
+    </row>
+    <row r="24" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+    </row>
+    <row r="25" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="s">
+      <c r="B25" s="11">
+        <f>MEDIAN(Tabela_1[idade])</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B26" s="9">
         <f>MEDIAN(Tabela_1[idade])</f>
         <v>22</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="s">
+    <row r="27" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="12">
-        <f>MEDIAN(Tabela_1[idade])</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="14">
+      <c r="B27" s="11">
         <f>MIN(Tabela_1[idade])</f>
         <v>19</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="12">
+    <row r="28" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="9">
         <f>MAX(Tabela_1[idade])</f>
         <v>43</v>
       </c>
     </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="15" t="s">
+    <row r="31" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="C31" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="15" t="s">
+    </row>
+    <row r="32" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="17">
+      <c r="B32" s="14">
         <f>COUNTIF(Tabela_1[quanto tempo você programa],#REF!)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="18">
-        <f t="shared" ref="C32:C36" si="1">B32/SUM($B$32:$B$36)</f>
+      <c r="C32" s="15">
+        <f t="shared" ref="C32:C36" si="0">B32/SUM($B$32:$B$36)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="17">
+    <row r="33" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="14">
         <f>COUNTIF(Tabela_1[quanto tempo você programa],A32)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="18">
-        <f t="shared" si="1"/>
+      <c r="C33" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="16" t="s">
+    <row r="34" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="14">
         <f>COUNTIF(Tabela_1[quanto tempo você programa],A33)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="18">
-        <f t="shared" si="1"/>
+      <c r="C34" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="16" t="s">
+    <row r="35" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="14">
         <f>COUNTIF(Tabela_1[quanto tempo você programa],A34)</f>
         <v>7</v>
       </c>
-      <c r="C35" s="18">
-        <f t="shared" si="1"/>
-        <v>0.2692307692</v>
-      </c>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="16" t="s">
+      <c r="C35" s="15">
+        <f t="shared" si="0"/>
+        <v>0.26923076923076922</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="14">
         <f>COUNTIF(Tabela_1[quanto tempo você programa],A35)</f>
         <v>19</v>
       </c>
-      <c r="C36" s="18">
-        <f t="shared" si="1"/>
-        <v>0.7307692308</v>
-      </c>
-    </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="15" t="s">
+      <c r="C36" s="15">
+        <f t="shared" si="0"/>
+        <v>0.73076923076923073</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="C39" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="16" t="s">
+    </row>
+    <row r="40" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="14">
         <f>COUNTIF(Tabela_1[nivel de experiência com python],A40)</f>
         <v>0</v>
       </c>
-      <c r="C40" s="18">
-        <f t="shared" ref="C40:C43" si="2">B40/SUM($B$40:$B$43)</f>
+      <c r="C40" s="15">
+        <f t="shared" ref="C40:C43" si="1">B40/SUM($B$40:$B$43)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="14">
         <f>COUNTIF(Tabela_1[nivel de experiência com python],A41)</f>
         <v>20</v>
       </c>
-      <c r="C41" s="18">
-        <f t="shared" si="2"/>
-        <v>0.6451612903</v>
-      </c>
-    </row>
-    <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="17">
+      <c r="C41" s="15">
+        <f t="shared" si="1"/>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="14">
         <f>COUNTIF(Tabela_1[nivel de experiência com python],A42)</f>
-        <v>10</v>
-      </c>
-      <c r="C42" s="18">
-        <f t="shared" si="2"/>
-        <v>0.3225806452</v>
-      </c>
-    </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="15">
+        <f t="shared" si="1"/>
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="14">
         <f>COUNTIF(Tabela_1[nivel de experiência com python],A43)</f>
         <v>1</v>
       </c>
-      <c r="C43" s="18">
-        <f t="shared" si="2"/>
-        <v>0.03225806452</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46" s="15" t="s">
+      <c r="C43" s="15">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="16" t="s">
+    </row>
+    <row r="47" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="14">
         <f>COUNTIF(Tabela_1[frequência que usa python],A47)</f>
         <v>2</v>
       </c>
-      <c r="C47" s="18">
-        <f t="shared" ref="C47:C51" si="3">B47/SUM($B$47:$B$51)</f>
-        <v>0.06451612903</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="16" t="s">
+      <c r="C47" s="15">
+        <f t="shared" ref="C47:C51" si="2">B47/SUM($B$47:$B$51)</f>
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="14">
         <f>COUNTIF(Tabela_1[frequência que usa python],A48)</f>
         <v>17</v>
       </c>
-      <c r="C48" s="18">
-        <f t="shared" si="3"/>
-        <v>0.5483870968</v>
-      </c>
-    </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="16" t="s">
+      <c r="C48" s="15">
+        <f t="shared" si="2"/>
+        <v>0.53125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="14">
         <f>COUNTIF(Tabela_1[frequência que usa python],A49)</f>
-        <v>8</v>
-      </c>
-      <c r="C49" s="18">
-        <f t="shared" si="3"/>
-        <v>0.2580645161</v>
-      </c>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="15">
+        <f t="shared" si="2"/>
+        <v>0.28125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="14">
         <f>COUNTIF(Tabela_1[frequência que usa python],A50)</f>
         <v>4</v>
       </c>
-      <c r="C50" s="18">
-        <f t="shared" si="3"/>
-        <v>0.1290322581</v>
-      </c>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B51" s="17">
+      <c r="C50" s="15">
+        <f t="shared" si="2"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="14">
         <f>COUNTIF(Tabela_1[frequência que usa python],A51)</f>
         <v>0</v>
       </c>
-      <c r="C51" s="18">
-        <f t="shared" si="3"/>
+      <c r="C51" s="15">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="15" t="s">
+    <row r="54" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C54" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="16" t="s">
+    </row>
+    <row r="55" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="14">
         <f>COUNTIF(Tabela_1[conhece clean code],A55)</f>
-        <v>29</v>
-      </c>
-      <c r="C55" s="18">
-        <f t="shared" ref="C55:C56" si="4">B55/SUM($B$55:$B$56)</f>
-        <v>0.935483871</v>
-      </c>
-    </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B56" s="17">
+      <c r="C55" s="15">
+        <f t="shared" ref="C55:C56" si="3">B55/SUM($B$55:$B$56)</f>
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="14">
         <f>COUNTIF(Tabela_1[conhece clean code],A56)</f>
         <v>2</v>
       </c>
-      <c r="C56" s="18">
-        <f t="shared" si="4"/>
-        <v>0.06451612903</v>
-      </c>
-    </row>
-    <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" s="20" t="s">
+      <c r="C56" s="15">
+        <f t="shared" si="3"/>
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C59" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="22" t="s">
+    </row>
+    <row r="60" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B60" s="20">
         <f>COUNTIF(Tabela_1[nivel em Clean Code],A60)</f>
         <v>1</v>
       </c>
-      <c r="C60" s="24">
-        <f t="shared" ref="C60:C63" si="5">B60/SUM($B$60:$B$63)</f>
-        <v>0.03225806452</v>
-      </c>
-    </row>
-    <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" s="22" t="s">
+      <c r="C60" s="21">
+        <f t="shared" ref="C60:C63" si="4">B60/SUM($B$60:$B$63)</f>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B61" s="20">
         <f>COUNTIF(Tabela_1[nivel em Clean Code],A61)</f>
         <v>15</v>
       </c>
-      <c r="C61" s="24">
-        <f t="shared" si="5"/>
-        <v>0.4838709677</v>
-      </c>
-    </row>
-    <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B62" s="23">
+      <c r="C61" s="21">
+        <f t="shared" si="4"/>
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="20">
         <f>COUNTIF(Tabela_1[nivel em Clean Code],A62)</f>
-        <v>15</v>
-      </c>
-      <c r="C62" s="24">
-        <f t="shared" si="5"/>
-        <v>0.4838709677</v>
-      </c>
-    </row>
-    <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="21">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B63" s="20">
         <f>COUNTIF(Tabela_1[nivel em Clean Code],A63)</f>
         <v>0</v>
       </c>
-      <c r="C63" s="24">
-        <f t="shared" si="5"/>
+      <c r="C63" s="21">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="s">
+    <row r="66" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+    </row>
+    <row r="67" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A67" s="9"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+    </row>
+    <row r="68" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A68" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C68" s="14">
+      <c r="B68" s="26"/>
+      <c r="C68" s="11">
         <f>COUNTIF(Tabela_1[importância da legibilidade no desenvolvimento],A68)</f>
         <v>0</v>
       </c>
-      <c r="D68" s="26">
-        <f t="shared" ref="D68:D70" si="6">C68/SUM($C$68:$C$70)</f>
+      <c r="D68" s="23">
+        <f t="shared" ref="D68:D70" si="5">C68/SUM($C$68:$C$70)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="11" t="s">
+    <row r="69" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12">
+      <c r="B69" s="9"/>
+      <c r="C69" s="9">
         <f>COUNTIF(Tabela_1[importância da legibilidade no desenvolvimento],A69)</f>
         <v>1</v>
       </c>
-      <c r="D69" s="27">
-        <f t="shared" si="6"/>
-        <v>0.03225806452</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="s">
+      <c r="D69" s="24">
+        <f t="shared" si="5"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14">
+      <c r="B70" s="11"/>
+      <c r="C70" s="11">
         <f>COUNTIF(Tabela_1[importância da legibilidade no desenvolvimento],A70)</f>
-        <v>30</v>
-      </c>
-      <c r="D70" s="26">
-        <f t="shared" si="6"/>
-        <v>0.9677419355</v>
-      </c>
-    </row>
-    <row r="76" ht="22.5" customHeight="1">
-      <c r="A76" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B76" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D70" s="23">
+        <f t="shared" si="5"/>
+        <v>0.96875</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C76" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" ht="22.5" customHeight="1">
-      <c r="A77" s="16" t="s">
+    </row>
+    <row r="77" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B77" s="17">
+      <c r="B77" s="14">
         <f>COUNTIF(Tabela_1[o que leu sobre Clean Code],A77)</f>
         <v>5</v>
       </c>
-      <c r="C77" s="18">
-        <f t="shared" ref="C77:C82" si="7">B77/SUM($B$77:$B$82)</f>
-        <v>0.2272727273</v>
-      </c>
-    </row>
-    <row r="78" ht="22.5" customHeight="1">
-      <c r="A78" s="16" t="s">
+      <c r="C77" s="15">
+        <f t="shared" ref="C77:C82" si="6">B77/SUM($B$77:$B$82)</f>
+        <v>0.21739130434782608</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B78" s="17">
+      <c r="B78" s="14">
         <f>COUNTIF(Tabela_1[o que leu sobre Clean Code],A78)</f>
-        <v>3</v>
-      </c>
-      <c r="C78" s="18">
-        <f t="shared" si="7"/>
-        <v>0.1363636364</v>
-      </c>
-    </row>
-    <row r="79" ht="22.5" customHeight="1">
-      <c r="A79" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B79" s="17">
+        <v>4</v>
+      </c>
+      <c r="C78" s="15">
+        <f t="shared" si="6"/>
+        <v>0.17391304347826086</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="14">
         <f>COUNTIF(Tabela_1[o que leu sobre Clean Code],A79)</f>
         <v>3</v>
       </c>
-      <c r="C79" s="18">
-        <f t="shared" si="7"/>
-        <v>0.1363636364</v>
-      </c>
-    </row>
-    <row r="80" ht="22.5" customHeight="1">
-      <c r="A80" s="16" t="s">
+      <c r="C79" s="15">
+        <f t="shared" si="6"/>
+        <v>0.13043478260869565</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B80" s="17">
+      <c r="B80" s="14">
         <f>COUNTIF(Tabela_1[o que leu sobre Clean Code],A80)</f>
         <v>6</v>
       </c>
-      <c r="C80" s="18">
-        <f t="shared" si="7"/>
-        <v>0.2727272727</v>
-      </c>
-    </row>
-    <row r="81" ht="22.5" customHeight="1">
-      <c r="A81" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="17">
+      <c r="C80" s="15">
+        <f t="shared" si="6"/>
+        <v>0.2608695652173913</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B81" s="14">
         <f>COUNTIF(Tabela_1[o que leu sobre Clean Code],A81)</f>
         <v>1</v>
       </c>
-      <c r="C81" s="18">
-        <f t="shared" si="7"/>
-        <v>0.04545454545</v>
-      </c>
-    </row>
-    <row r="82" ht="22.5" customHeight="1">
-      <c r="A82" s="16" t="s">
+      <c r="C81" s="15">
+        <f t="shared" si="6"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B82" s="17">
+      <c r="B82" s="14">
         <f>COUNTIF(Tabela_1[o que leu sobre Clean Code],A82)</f>
         <v>4</v>
       </c>
-      <c r="C82" s="18">
-        <f t="shared" si="7"/>
-        <v>0.1818181818</v>
+      <c r="C82" s="15">
+        <f t="shared" si="6"/>
+        <v>0.17391304347826086</v>
       </c>
     </row>
   </sheetData>
@@ -3597,40 +5633,42 @@
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A68:B68"/>
   </mergeCells>
-  <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="C32:C36 C40:C43 C47:C51 C55:C56 C60:C63 C77:C82">
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="C32:C36 C40:C43 C47:C51 C55:C56 C60:C63 C77:C82" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>AND(ISNUMBER(C32),(NOT(OR(NOT(ISERROR(DATEVALUE(C32))), AND(ISNUMBER(C32), LEFT(CELL("format", C32))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId3"/>
   <tableParts count="6">
-    <tablePart r:id="rId10"/>
-    <tablePart r:id="rId11"/>
-    <tablePart r:id="rId12"/>
-    <tablePart r:id="rId13"/>
-    <tablePart r:id="rId14"/>
-    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.13"/>
-    <col customWidth="1" min="5" max="5" width="27.25"/>
-    <col customWidth="1" min="6" max="6" width="29.25"/>
-    <col customWidth="1" min="7" max="7" width="25.13"/>
-    <col customWidth="1" min="8" max="8" width="20.38"/>
-    <col customWidth="1" min="9" max="9" width="21.0"/>
-    <col customWidth="1" min="10" max="11" width="37.63"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="27.21875" customWidth="1"/>
+    <col min="6" max="6" width="29.21875" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="11" width="37.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3665,18 +5703,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>12</v>
@@ -3700,18 +5738,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>18</v>
@@ -3735,18 +5773,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>12</v>
@@ -3770,18 +5808,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
@@ -3805,18 +5843,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>25</v>
@@ -3840,18 +5878,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>12</v>
@@ -3875,18 +5913,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>12</v>
@@ -3910,18 +5948,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>25</v>
@@ -3945,18 +5983,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>12</v>
@@ -3980,18 +6018,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>12</v>
@@ -4015,18 +6053,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>12</v>
@@ -4050,18 +6088,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
+    <row r="13" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>12</v>
@@ -4078,25 +6116,25 @@
       <c r="I13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="9" t="s">
-        <v>43</v>
+      <c r="J13" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
+    <row r="14" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>12</v>
@@ -4120,18 +6158,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
+    <row r="15" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>12</v>
@@ -4155,18 +6193,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
+    <row r="16" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="4">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>25</v>
@@ -4190,18 +6228,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" ht="22.5" customHeight="1">
+    <row r="17" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="4">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>18</v>
@@ -4225,18 +6263,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" ht="22.5" customHeight="1">
+    <row r="18" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>12</v>
@@ -4253,25 +6291,25 @@
       <c r="I18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="9" t="s">
-        <v>49</v>
+      <c r="J18" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" ht="22.5" customHeight="1">
+    <row r="19" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>25</v>
@@ -4288,25 +6326,25 @@
       <c r="I19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>49</v>
+      <c r="J19" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
+    <row r="20" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>25</v>
@@ -4330,18 +6368,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" ht="22.5" customHeight="1">
+    <row r="21" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>25</v>
@@ -4365,18 +6403,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" ht="22.5" customHeight="1">
+    <row r="22" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>12</v>
@@ -4400,18 +6438,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" ht="22.5" customHeight="1">
+    <row r="23" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>12</v>
@@ -4435,18 +6473,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" ht="22.5" customHeight="1">
+    <row r="24" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>12</v>
@@ -4470,18 +6508,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" ht="22.5" customHeight="1">
+    <row r="25" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>18</v>
@@ -4498,25 +6536,25 @@
       <c r="I25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>56</v>
+      <c r="J25" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" ht="22.5" customHeight="1">
+    <row r="26" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>18</v>
@@ -4540,18 +6578,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" ht="22.5" customHeight="1">
+    <row r="27" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>12</v>
@@ -4575,18 +6613,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
+    <row r="28" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>12</v>
@@ -4610,18 +6648,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" ht="22.5" customHeight="1">
+    <row r="29" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D29" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>12</v>
@@ -4645,18 +6683,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" ht="22.5" customHeight="1">
+    <row r="30" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>12</v>
@@ -4680,18 +6718,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" ht="22.5" customHeight="1">
+    <row r="31" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>12</v>
@@ -4708,25 +6746,25 @@
       <c r="I31" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>49</v>
+      <c r="J31" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" ht="22.5" customHeight="1">
+    <row r="32" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>25</v>
@@ -4750,31 +6788,67 @@
         <v>17</v>
       </c>
     </row>
+    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33">
+        <v>9</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="22.75"/>
-    <col customWidth="1" min="6" max="6" width="24.75"/>
-    <col customWidth="1" min="7" max="7" width="20.63"/>
-    <col customWidth="1" min="8" max="8" width="15.88"/>
-    <col customWidth="1" min="9" max="9" width="16.5"/>
-    <col customWidth="1" min="10" max="10" width="21.75"/>
-    <col customWidth="1" min="11" max="11" width="36.0"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="6" max="6" width="24.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" customWidth="1"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1"/>
+    <col min="11" max="11" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4809,18 +6883,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>12</v>
@@ -4844,18 +6918,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>18</v>
@@ -4879,18 +6953,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>12</v>
@@ -4914,18 +6988,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>18</v>
@@ -4949,18 +7023,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -4984,18 +7058,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>12</v>
@@ -5019,18 +7093,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>12</v>
@@ -5054,18 +7128,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -5089,18 +7163,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>12</v>
@@ -5124,18 +7198,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>12</v>
@@ -5159,18 +7233,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>12</v>
@@ -5194,18 +7268,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>12</v>
@@ -5229,18 +7303,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>12</v>
@@ -5264,18 +7338,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>12</v>
@@ -5299,18 +7373,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -5334,18 +7408,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>18</v>
@@ -5369,18 +7443,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>12</v>
@@ -5404,18 +7478,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -5439,18 +7513,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -5474,18 +7548,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -5509,18 +7583,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>12</v>
@@ -5544,18 +7618,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>12</v>
@@ -5579,18 +7653,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>12</v>
@@ -5614,18 +7688,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>18</v>
@@ -5649,18 +7723,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>18</v>
@@ -5684,18 +7758,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>12</v>
@@ -5719,18 +7793,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>12</v>
@@ -5754,18 +7828,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D29" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>12</v>
@@ -5789,18 +7863,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>12</v>
@@ -5824,18 +7898,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>12</v>
@@ -5859,18 +7933,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>25</v>
@@ -5894,18 +7968,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>18</v>
@@ -5930,6 +8004,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>